--- a/template baru.xlsx
+++ b/template baru.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAFBAB9-7D83-4D3F-8DF0-24B3B6436818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E844D8D-1060-4FAF-AA2C-E703D510EB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="215">
   <si>
     <t>kode</t>
   </si>
@@ -163,12 +163,6 @@
     <t>Iin Tri Rahayu</t>
   </si>
   <si>
-    <t>20000011A04</t>
-  </si>
-  <si>
-    <t>Bahasa Arab I 2</t>
-  </si>
-  <si>
     <t>nii</t>
   </si>
   <si>
@@ -179,12 +173,6 @@
   </si>
   <si>
     <t>Tristiardi Ardi Ardani</t>
-  </si>
-  <si>
-    <t>20000011A05</t>
-  </si>
-  <si>
-    <t>Bahasa Arab II 2</t>
   </si>
   <si>
     <t>hls</t>
@@ -1402,10 +1390,10 @@
   <dimension ref="A1:P56"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" customWidth="1"/>
     <col min="2" max="2" width="37.7265625" customWidth="1"/>
     <col min="3" max="14" width="13.54296875" customWidth="1"/>
-    <col min="15" max="15" width="30.453125" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="44" customWidth="1"/>
     <col min="17" max="24" width="13.54296875" customWidth="1"/>
   </cols>
@@ -1647,181 +1635,181 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>47</v>
+      <c r="D6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C7" s="6">
         <v>2</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>53</v>
+      <c r="D7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>58</v>
+      <c r="A8" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="C8" s="6">
         <v>2</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>65</v>
+      <c r="A9" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>20</v>
@@ -1830,92 +1818,92 @@
         <v>32</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C10" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>71</v>
+        <v>51</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C11" s="6">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>20</v>
@@ -1924,233 +1912,233 @@
         <v>28</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="13" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>72</v>
+        <v>33</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>84</v>
+        <v>33</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C13" s="6">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>91</v>
+        <v>43</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C14" s="6">
-        <v>3</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>92</v>
+        <v>2</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C15" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="A16" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>60</v>
+      <c r="D16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>20</v>
@@ -2159,45 +2147,45 @@
         <v>30</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="A17" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>108</v>
+      <c r="H17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>20</v>
@@ -2206,327 +2194,327 @@
         <v>26</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>112</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>16</v>
+        <v>109</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>62</v>
+        <v>3</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>85</v>
+        <v>121</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C20" s="15">
         <v>3</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>100</v>
+        <v>87</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>100</v>
+        <v>128</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="14" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C21" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="14" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C22" s="15">
         <v>3</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>91</v>
+      <c r="D22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>133</v>
+        <v>113</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C23" s="15">
         <v>2</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>108</v>
+      <c r="D23" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" s="15">
-        <v>3</v>
+        <v>142</v>
+      </c>
+      <c r="C24" s="16">
+        <v>1</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>117</v>
+        <v>19</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>20</v>
@@ -2535,287 +2523,243 @@
         <v>16</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="15">
-        <v>2</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="C25" s="16">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="16">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>19</v>
+      <c r="A26" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>19</v>
+        <v>129</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C27" s="16">
-        <v>3</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>126</v>
+      <c r="A27" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>33</v>
+        <v>128</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="6">
+        <v>155</v>
+      </c>
+      <c r="C28" s="18">
         <v>2</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="21"/>
       <c r="O28" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="6">
-        <v>2</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C29" s="18">
+        <v>0</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="21"/>
       <c r="O29" s="11" t="s">
         <v>29</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>159</v>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23" t="s">
+        <v>160</v>
       </c>
       <c r="C30" s="18">
-        <v>2</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
+        <v>4</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
       <c r="J30" s="20"/>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
       <c r="M30" s="21"/>
       <c r="O30" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="18">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="C31" s="7">
+        <v>2</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
       <c r="J31" s="20"/>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -2824,23 +2768,23 @@
         <v>41</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="18">
-        <v>4</v>
-      </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
+      <c r="C32" s="7">
+        <v>2</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
       <c r="J32" s="20"/>
       <c r="K32" s="20"/>
       <c r="L32" s="20"/>
@@ -2849,19 +2793,25 @@
         <v>37</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="14" t="s">
         <v>166</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="C33" s="7">
         <v>2</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="D33" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>109</v>
+      </c>
       <c r="F33" s="7"/>
       <c r="G33" s="20"/>
       <c r="H33" s="20"/>
@@ -2869,89 +2819,91 @@
       <c r="J33" s="20"/>
       <c r="K33" s="20"/>
       <c r="L33" s="20"/>
-      <c r="M33" s="21"/>
+      <c r="M33" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="O33" s="24" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14" t="s">
-        <v>168</v>
+      <c r="A34" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="C34" s="7">
         <v>2</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
+      <c r="D34" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="7"/>
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
       <c r="K34" s="20"/>
       <c r="L34" s="20"/>
-      <c r="M34" s="21"/>
+      <c r="M34" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="O34" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P34" s="25" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>171</v>
+      <c r="A35" s="13"/>
+      <c r="B35" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="C35" s="7">
         <v>2</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="7"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
       <c r="L35" s="20"/>
-      <c r="M35" s="21" t="s">
-        <v>172</v>
-      </c>
+      <c r="M35" s="21"/>
       <c r="O35" s="24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="B36" s="26" t="s">
+      <c r="A36" s="13" t="s">
         <v>175</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="C36" s="7">
         <v>2</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="F36" s="28"/>
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
       <c r="I36" s="20"/>
@@ -2959,25 +2911,31 @@
       <c r="K36" s="20"/>
       <c r="L36" s="20"/>
       <c r="M36" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="O36" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="O36" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="P36" s="25" t="s">
-        <v>176</v>
-      </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13" t="s">
-        <v>177</v>
+      <c r="A37" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>179</v>
       </c>
       <c r="C37" s="7">
         <v>2</v>
       </c>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
+      <c r="D37" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="F37" s="28"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
@@ -2985,30 +2943,28 @@
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
       <c r="L37" s="20"/>
-      <c r="M37" s="21"/>
+      <c r="M37" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="O37" s="24" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P37" s="25" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>182</v>
       </c>
       <c r="C38" s="7">
         <v>2</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>85</v>
-      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
       <c r="F38" s="28"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
@@ -3016,32 +2972,26 @@
       <c r="J38" s="20"/>
       <c r="K38" s="20"/>
       <c r="L38" s="20"/>
-      <c r="M38" s="21" t="s">
-        <v>172</v>
-      </c>
+      <c r="M38" s="21"/>
       <c r="O38" s="24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>183</v>
+      <c r="A39" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="C39" s="7">
         <v>2</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>85</v>
-      </c>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
       <c r="F39" s="28"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
@@ -3049,55 +2999,61 @@
       <c r="J39" s="20"/>
       <c r="K39" s="20"/>
       <c r="L39" s="20"/>
-      <c r="M39" s="21" t="s">
-        <v>172</v>
-      </c>
+      <c r="M39" s="21"/>
       <c r="O39" s="24" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="29" t="s">
-        <v>186</v>
+      <c r="A40" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>188</v>
       </c>
       <c r="C40" s="7">
         <v>2</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="20"/>
+      <c r="D40" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>104</v>
+      </c>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
       <c r="K40" s="20"/>
       <c r="L40" s="20"/>
-      <c r="M40" s="21"/>
+      <c r="M40" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="O40" s="24" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>189</v>
+      <c r="A41" s="7"/>
+      <c r="B41" s="33" t="s">
+        <v>190</v>
       </c>
       <c r="C41" s="7">
         <v>2</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
       <c r="F41" s="28"/>
       <c r="G41" s="20"/>
       <c r="H41" s="20"/>
@@ -3107,53 +3063,55 @@
       <c r="L41" s="20"/>
       <c r="M41" s="21"/>
       <c r="O41" s="24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B42" s="32" t="s">
+      <c r="A42" s="34" t="s">
         <v>192</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>193</v>
       </c>
       <c r="C42" s="7">
         <v>2</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>108</v>
+        <v>128</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
+        <v>104</v>
+      </c>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
       <c r="K42" s="20"/>
       <c r="L42" s="20"/>
       <c r="M42" s="21" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="O42" s="24" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="7"/>
-      <c r="B43" s="33" t="s">
-        <v>194</v>
+      <c r="A43" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>196</v>
       </c>
       <c r="C43" s="7">
         <v>2</v>
@@ -3169,146 +3127,98 @@
       <c r="L43" s="20"/>
       <c r="M43" s="21"/>
       <c r="O43" s="24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>197</v>
+      <c r="A44" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>199</v>
       </c>
       <c r="C44" s="7">
         <v>2</v>
       </c>
-      <c r="D44" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
+      <c r="D44" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="F44" s="38"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
       <c r="K44" s="20"/>
       <c r="L44" s="20"/>
       <c r="M44" s="21" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="P44" s="35" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>203</v>
       </c>
       <c r="C45" s="7">
         <v>2</v>
       </c>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
+      <c r="D45" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="7"/>
       <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
+      <c r="H45" s="39"/>
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
       <c r="K45" s="20"/>
       <c r="L45" s="20"/>
-      <c r="M45" s="21"/>
+      <c r="M45" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="O45" s="20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P45" s="36" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="B46" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="C46" s="7">
-        <v>2</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="F46" s="38"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="21" t="s">
-        <v>172</v>
-      </c>
       <c r="O46" s="20" t="s">
         <v>17</v>
       </c>
       <c r="P46" s="34" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="B47" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="C47" s="7">
-        <v>2</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="21" t="s">
-        <v>172</v>
-      </c>
       <c r="O47" s="40" t="s">
         <v>18</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="23"/>
       <c r="B48" s="23" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C48" s="7">
         <v>2</v>
@@ -3324,10 +3234,10 @@
       <c r="L48" s="20"/>
       <c r="M48" s="21"/>
       <c r="O48" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P48" s="41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="15:16">
@@ -3335,47 +3245,47 @@
         <v>19</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="15:16">
       <c r="O50" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P50" s="42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="15:16">
       <c r="O51" s="43" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="P51" s="44" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="15:16">
       <c r="O52" s="43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="P52" s="44" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="15:16">
       <c r="O53" s="43" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P53" s="44" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="15:16">
       <c r="O54" s="43" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P54" s="44" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="15:16">
@@ -3383,7 +3293,7 @@
         <v>25</v>
       </c>
       <c r="P55" s="44" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="15:16">
@@ -3391,7 +3301,7 @@
         <v>42</v>
       </c>
       <c r="P56" s="46" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/template baru.xlsx
+++ b/template baru.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E844D8D-1060-4FAF-AA2C-E703D510EB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AD6FB6-2389-4781-98A5-8C7673423A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="215">
   <si>
     <t>kode</t>
   </si>
@@ -490,21 +490,9 @@
     <t>Rahmatika Sari Amalia</t>
   </si>
   <si>
-    <t>22040111D35</t>
-  </si>
-  <si>
-    <t>PKL 2</t>
-  </si>
-  <si>
     <t>andik roni irawan</t>
   </si>
   <si>
-    <t>22040111D38</t>
-  </si>
-  <si>
-    <t>Komprehensif 0</t>
-  </si>
-  <si>
     <t>Yahya</t>
   </si>
   <si>
@@ -671,6 +659,18 @@
   </si>
   <si>
     <t>Bahrun Amiq</t>
+  </si>
+  <si>
+    <t>Psikologi Kepribadian 6 2</t>
+  </si>
+  <si>
+    <t>22040111D042</t>
+  </si>
+  <si>
+    <t>Psikologi Dasar 6 2</t>
+  </si>
+  <si>
+    <t>22040111D012</t>
   </si>
 </sst>
 </file>
@@ -934,7 +934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -977,9 +977,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1500,7 +1497,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>25</v>
@@ -1829,7 +1826,7 @@
         <v>76</v>
       </c>
       <c r="C10" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>51</v>
@@ -2668,25 +2665,45 @@
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="C28" s="18">
-        <v>2</v>
-      </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="21"/>
+      <c r="A28" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="O28" s="11" t="s">
         <v>129</v>
       </c>
@@ -2695,25 +2712,45 @@
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C29" s="18">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="21"/>
+      <c r="A29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="6">
+        <v>3</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="O29" s="11" t="s">
         <v>29</v>
       </c>
@@ -2722,9 +2759,9 @@
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23" t="s">
-        <v>160</v>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="C30" s="18">
         <v>4</v>
@@ -2735,21 +2772,21 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="21"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="20"/>
       <c r="O30" s="11" t="s">
         <v>139</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="14"/>
       <c r="B31" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C31" s="7">
         <v>2</v>
@@ -2757,24 +2794,24 @@
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="21"/>
-      <c r="O31" s="22" t="s">
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="20"/>
+      <c r="O31" s="21" t="s">
         <v>41</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="14"/>
       <c r="B32" s="14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C32" s="7">
         <v>2</v>
@@ -2782,26 +2819,26 @@
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="21"/>
-      <c r="O32" s="22" t="s">
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="20"/>
+      <c r="O32" s="21" t="s">
         <v>37</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>167</v>
+        <v>162</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>163</v>
       </c>
       <c r="C33" s="7">
         <v>2</v>
@@ -2813,28 +2850,28 @@
         <v>109</v>
       </c>
       <c r="F33" s="7"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O33" s="24" t="s">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O33" s="23" t="s">
         <v>72</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>171</v>
+      <c r="A34" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>167</v>
       </c>
       <c r="C34" s="7">
         <v>2</v>
@@ -2846,53 +2883,53 @@
         <v>108</v>
       </c>
       <c r="F34" s="7"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O34" s="24" t="s">
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O34" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="P34" s="25" t="s">
-        <v>165</v>
+      <c r="P34" s="24" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="13"/>
       <c r="B35" s="13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C35" s="7">
         <v>2</v>
       </c>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="21"/>
-      <c r="O35" s="24" t="s">
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="20"/>
+      <c r="O35" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="P35" s="25" t="s">
-        <v>169</v>
+      <c r="P35" s="24" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="13" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C36" s="7">
         <v>2</v>
@@ -2903,29 +2940,29 @@
       <c r="E36" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="21" t="s">
+      <c r="F36" s="27"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="O36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="P36" s="25" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>179</v>
+        <v>174</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>175</v>
       </c>
       <c r="C37" s="7">
         <v>2</v>
@@ -2936,83 +2973,83 @@
       <c r="E37" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F37" s="28"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O37" s="24" t="s">
+      <c r="F37" s="27"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O37" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="P37" s="25" t="s">
-        <v>174</v>
+      <c r="P37" s="24" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>182</v>
+        <v>177</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>178</v>
       </c>
       <c r="C38" s="7">
         <v>2</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="21"/>
-      <c r="O38" s="24" t="s">
+      <c r="F38" s="27"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="20"/>
+      <c r="O38" s="23" t="s">
         <v>73</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>185</v>
+      <c r="A39" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>181</v>
       </c>
       <c r="C39" s="7">
         <v>2</v>
       </c>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="21"/>
-      <c r="O39" s="24" t="s">
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="20"/>
+      <c r="O39" s="23" t="s">
         <v>63</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B40" s="32" t="s">
-        <v>188</v>
+        <v>183</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>184</v>
       </c>
       <c r="C40" s="7">
         <v>2</v>
@@ -3026,55 +3063,55 @@
       <c r="F40" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O40" s="24" t="s">
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O40" s="23" t="s">
         <v>67</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="7"/>
-      <c r="B41" s="33" t="s">
-        <v>190</v>
+      <c r="B41" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="C41" s="7">
         <v>2</v>
       </c>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="21"/>
-      <c r="O41" s="24" t="s">
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="20"/>
+      <c r="O41" s="23" t="s">
         <v>62</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="B42" s="33" t="s">
-        <v>193</v>
+      <c r="A42" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="C42" s="7">
         <v>2</v>
@@ -3088,137 +3125,137 @@
       <c r="F42" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O42" s="24" t="s">
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O42" s="23" t="s">
         <v>55</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>196</v>
+      <c r="A43" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>192</v>
       </c>
       <c r="C43" s="7">
         <v>2</v>
       </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="21"/>
-      <c r="O43" s="24" t="s">
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="20"/>
+      <c r="O43" s="23" t="s">
         <v>56</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="B44" s="30" t="s">
-        <v>199</v>
+      <c r="A44" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B44" s="29" t="s">
+        <v>195</v>
       </c>
       <c r="C44" s="7">
         <v>2</v>
       </c>
-      <c r="D44" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="F44" s="38"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O44" s="20" t="s">
+      <c r="D44" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" s="37"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O44" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="P44" s="35" t="s">
-        <v>194</v>
+      <c r="P44" s="34" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>203</v>
+      <c r="A45" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="29" t="s">
+        <v>199</v>
       </c>
       <c r="C45" s="7">
         <v>2</v>
       </c>
-      <c r="D45" s="37" t="s">
-        <v>200</v>
+      <c r="D45" s="36" t="s">
+        <v>196</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F45" s="7"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="O45" s="20" t="s">
+      <c r="G45" s="19"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O45" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="P45" s="36" t="s">
+      <c r="P45" s="35" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="O46" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="P46" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
-      <c r="O46" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="P46" s="34" t="s">
+    <row r="47" spans="1:16">
+      <c r="O47" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="P47" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="O47" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23" t="s">
-        <v>205</v>
       </c>
       <c r="C48" s="7">
         <v>2</v>
@@ -3226,18 +3263,18 @@
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="21"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="20"/>
       <c r="O48" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="P48" s="41" t="s">
-        <v>206</v>
+      <c r="P48" s="40" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="49" spans="15:16">
@@ -3245,63 +3282,63 @@
         <v>19</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="15:16">
       <c r="O50" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P50" s="42" t="s">
+      <c r="P50" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="15:16">
+      <c r="O51" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="P51" s="43" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="15:16">
+      <c r="O52" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="P52" s="43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="15:16">
+      <c r="O53" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="P53" s="43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="54" spans="15:16">
+      <c r="O54" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="P54" s="43" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="51" spans="15:16">
-      <c r="O51" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="P51" s="44" t="s">
+    <row r="55" spans="15:16">
+      <c r="O55" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="P55" s="43" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="15:16">
-      <c r="O52" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="P52" s="44" t="s">
+    <row r="56" spans="15:16">
+      <c r="O56" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="P56" s="45" t="s">
         <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="15:16">
-      <c r="O53" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="P53" s="44" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="15:16">
-      <c r="O54" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="P54" s="44" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="55" spans="15:16">
-      <c r="O55" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="P55" s="44" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="56" spans="15:16">
-      <c r="O56" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="P56" s="46" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
